--- a/data/availability/projects/misr-italia-properties/kai-sokhna.xlsx
+++ b/data/availability/projects/misr-italia-properties/kai-sokhna.xlsx
@@ -554,7 +554,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Studio</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -935,7 +935,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Studio</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1020,7 +1020,6 @@
       <c r="G3" t="n">
         <v>83</v>
       </c>
-      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1077,7 +1076,6 @@
       <c r="G4" t="n">
         <v>141</v>
       </c>
-      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1134,7 +1132,6 @@
       <c r="G5" t="n">
         <v>147</v>
       </c>
-      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1191,7 +1188,6 @@
       <c r="G6" t="n">
         <v>222</v>
       </c>
-      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
           <t>Landscape</t>
